--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:59</t>
+    <t xml:space="preserve">2026-08-17 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 22:12</t>
+    <t xml:space="preserve">2026-09-06 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
